--- a/nord-kivu/sortie/zs/Lubero/Tableaux_ZS_Lubero_20261014.xlsx
+++ b/nord-kivu/sortie/zs/Lubero/Tableaux_ZS_Lubero_20261014.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cas" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bulletin des aires'!$A$1:$P$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bulletin des aires'!$A$1:$P$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cas'!$A$1:$S$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -452,11 +452,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -558,27 +558,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kakonze</t>
+          <t>Baraka</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>12</v>
-      </c>
-      <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
@@ -588,27 +582,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kasugho</t>
+          <t>Hgr Lubero</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
@@ -618,25 +606,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kavetya</t>
+          <t>Kakonze</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jaune</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
       <c r="G4" t="n">
-        <v>33</v>
+        <v>12</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -645,27 +636,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kipese</t>
+          <t>Kasala</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
@@ -675,25 +660,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lubero</t>
+          <t>Kasalala</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Verte</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>69</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -702,27 +684,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lubero-Cite</t>
+          <t>Kasima</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
@@ -732,32 +708,344 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Kasinzwe</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kassalala</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kasugho</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Katolo</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kavetya</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Jaune</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>33</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Kipese</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Lub-Cite</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Lubero</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Verte</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>69</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Lubero-Cite</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Lukanga</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Mubana</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Mulo</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Vunyakondomi</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Jaune</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C20" t="n">
         <v>6</v>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>35</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I20" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P8"/>
+  <autoFilter ref="A1:P20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
